--- a/Thread_1/data/2023/MSB/scoring/MSB_Gap_Score.xlsx
+++ b/Thread_1/data/2023/MSB/scoring/MSB_Gap_Score.xlsx
@@ -448,10 +448,10 @@
         <v>0.0214168039538715</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0.001879699248120301</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0214168039538715</v>
+        <v>0.0232965032019918</v>
       </c>
     </row>
   </sheetData>
